--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T11:48:09+00:00</t>
+    <t>2026-09-14T12:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:20:33+00:00</t>
+    <t>2026-09-14T12:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Genliste des Panels: FusionPlex Archer Lung V2 (17 Gene, Fusionsanalyse). Kodiert als HGNC-Gensymbole; TODO:REVIEW HGNC-ID-Mapping.</t>
+    <t>Genliste des Panels: FusionPlex Archer Lung V2 (17 Gene, Fusionsanalyse). Kodiert mit stabilen HGNC-IDs (System genenames.org/geneId), Displays = aktuelle HGNC-Symbole.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -102,54 +102,105 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>HGNC:427</t>
+  </si>
+  <si>
     <t>ALK</t>
   </si>
   <si>
+    <t>HGNC:1097</t>
+  </si>
+  <si>
     <t>BRAF</t>
   </si>
   <si>
+    <t>HGNC:3236</t>
+  </si>
+  <si>
     <t>EGFR</t>
   </si>
   <si>
+    <t>HGNC:3430</t>
+  </si>
+  <si>
     <t>ERBB2</t>
   </si>
   <si>
+    <t>HGNC:3688</t>
+  </si>
+  <si>
     <t>FGFR1</t>
   </si>
   <si>
+    <t>HGNC:3689</t>
+  </si>
+  <si>
     <t>FGFR2</t>
   </si>
   <si>
+    <t>HGNC:3690</t>
+  </si>
+  <si>
     <t>FGFR3</t>
   </si>
   <si>
+    <t>HGNC:6407</t>
+  </si>
+  <si>
     <t>KRAS</t>
   </si>
   <si>
+    <t>HGNC:7029</t>
+  </si>
+  <si>
     <t>MET</t>
   </si>
   <si>
+    <t>HGNC:7997</t>
+  </si>
+  <si>
     <t>NRG1</t>
   </si>
   <si>
+    <t>HGNC:8031</t>
+  </si>
+  <si>
     <t>NTRK1</t>
   </si>
   <si>
+    <t>HGNC:8032</t>
+  </si>
+  <si>
     <t>NTRK2</t>
   </si>
   <si>
+    <t>HGNC:8033</t>
+  </si>
+  <si>
     <t>NTRK3</t>
   </si>
   <si>
+    <t>HGNC:29919</t>
+  </si>
+  <si>
     <t>NUTM1</t>
   </si>
   <si>
+    <t>HGNC:8975</t>
+  </si>
+  <si>
     <t>PIK3CA</t>
   </si>
   <si>
+    <t>HGNC:9967</t>
+  </si>
+  <si>
     <t>RET</t>
   </si>
   <si>
+    <t>HGNC:10261</t>
+  </si>
+  <si>
     <t>ROS1</t>
   </si>
   <si>
@@ -159,7 +210,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://www.genenames.org</t>
+    <t>http://www.genenames.org/geneId</t>
   </si>
 </sst>
 </file>
@@ -443,151 +494,151 @@
         <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:53:39+00:00</t>
+    <t>2026-09-14T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
+++ b/branches/migration/2026.0.1-template-v0.13.2/ValueSet-mii-vs-mtb-panel-archer-lung-v2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:42:50+00:00</t>
+    <t>2026-09-14T17:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
